--- a/23-06-26/Salman.xlsx
+++ b/23-06-26/Salman.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E349EF1-D3EE-40B1-85D6-BA168B3EF155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6EFB604-38F9-41F3-B0E6-19BD6B511126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23466,7 +23466,7 @@
       </c>
       <c r="U15" s="164">
         <f>+'2'!P35</f>
-        <v>2955.6224995500002</v>
+        <v>2856.9881614500005</v>
       </c>
       <c r="XFD15" t="s">
         <v>81</v>
@@ -23499,11 +23499,11 @@
       <c r="G16" s="114"/>
       <c r="H16" s="172">
         <f>+'1'!H16+'2'!H16+'4'!H16+'3'!H16+'5'!H16+'6'!H16+'7'!H16+'8'!H16+'9'!H16+'10'!H16+'11'!H16+'12'!H16+'13'!H16+'14'!H16+'15'!H16+'16'!H16</f>
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="I16" s="1">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>1993.575</v>
+        <v>1049.25</v>
       </c>
       <c r="J16" s="172">
         <f>+'1'!J16+'2'!J16+'4'!J16+'3'!J16+'5'!J16+'6'!J16+'7'!J16+'8'!J16+'9'!J16+'10'!J16+'11'!J16+'12'!J16+'13'!J16+'14'!J16+'15'!J16+'16'!J16+'17'!J16+'18'!J16</f>
@@ -23515,23 +23515,23 @@
       </c>
       <c r="L16" s="175">
         <f>+'1'!L16+'2'!L16+'4'!L16+'3'!L16+'5'!L16+'6'!L16+'7'!L16+'8'!L16+'9'!L16+'10'!L16</f>
-        <v>159.48599999999999</v>
+        <v>83.94</v>
       </c>
       <c r="M16" s="106">
         <f>I16-K16-L16</f>
-        <v>1834.0889999999999</v>
+        <v>965.31</v>
       </c>
       <c r="N16" s="101">
         <f>+'1'!N16+'2'!N16+'4'!N16+'3'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16</f>
-        <v>368.74842000000001</v>
+        <v>193.06200000000001</v>
       </c>
       <c r="O16" s="101">
         <f>+'1'!O16+'2'!O16+'4'!O16+'3'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16</f>
-        <v>31.517371499999999</v>
+        <v>5.7918599999999998</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="0">M16+N16+O16</f>
-        <v>2234.3547914999999</v>
+        <v>1164.1638599999999</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="T16" s="163" t="str">
@@ -23539,8 +23539,8 @@
         <v>Customer Name : Munchies Mart</v>
       </c>
       <c r="U16" s="164">
-        <f>+'4'!P35</f>
-        <v>880.2282249000001</v>
+        <f>+'3'!P35</f>
+        <v>3309.6730752000008</v>
       </c>
       <c r="XFD16" t="s">
         <v>82</v>
@@ -23573,15 +23573,15 @@
       <c r="G17" s="114"/>
       <c r="H17" s="172">
         <f>+'1'!H17+'2'!H17+'4'!H17+'3'!H17+'5'!H17+'6'!H17+'7'!H17+'8'!H17+'9'!H17+'10'!H17+'11'!H17+'12'!H17+'13'!H17+'14'!H17+'15'!H17+'16'!H17</f>
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" ref="I17:I23" si="1">(G17*D17)*F17+H17*F17</f>
-        <v>1993.575</v>
+        <v>1049.25</v>
       </c>
       <c r="J17" s="172">
         <f>+'1'!J17+'2'!J17+'4'!J17+'3'!J17+'5'!J17+'6'!J17+'7'!J17+'8'!J17+'9'!J17+'10'!J17+'11'!J17+'12'!J17+'13'!J17+'14'!J17+'15'!J17+'16'!J17+'17'!J17+'18'!J17</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K17" s="172">
         <f>+'1'!K17+'2'!K17+'4'!K17+'3'!K17+'5'!K17+'6'!K17+'7'!K17+'8'!K17+'9'!K17+'10'!K17</f>
@@ -23589,23 +23589,23 @@
       </c>
       <c r="L17" s="175">
         <f>+'1'!L17+'2'!L17+'4'!L17+'3'!L17+'5'!L17+'6'!L17+'7'!L17+'8'!L17+'9'!L17+'10'!L17</f>
-        <v>159.48599999999999</v>
+        <v>83.94</v>
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="2">I17-K17-L17</f>
-        <v>1834.0889999999999</v>
+        <v>965.31</v>
       </c>
       <c r="N17" s="101">
         <f>+'1'!N17+'2'!N17+'4'!N17+'3'!N17+'5'!N17+'6'!N17+'7'!N17+'8'!N17+'9'!N17+'10'!N17</f>
-        <v>401.27517</v>
+        <v>214.047</v>
       </c>
       <c r="O17" s="101">
         <f>+'1'!O17+'2'!O17+'4'!O17+'3'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17</f>
-        <v>31.868870250000001</v>
+        <v>5.8967849999999995</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="0"/>
-        <v>2267.2330402499997</v>
+        <v>1185.2537849999999</v>
       </c>
       <c r="S17" s="64"/>
       <c r="T17" s="163" t="str">
@@ -23613,8 +23613,8 @@
         <v xml:space="preserve">Customer Name : Ajmar Bakery </v>
       </c>
       <c r="U17" s="164">
-        <f>+'3'!P35</f>
-        <v>3309.6730752000008</v>
+        <f>+'4'!P35</f>
+        <v>880.2282249000001</v>
       </c>
       <c r="XFD17" t="s">
         <v>83</v>
@@ -23647,15 +23647,15 @@
       <c r="G18" s="114"/>
       <c r="H18" s="172">
         <f>+'1'!H18+'2'!H18+'4'!H18+'3'!H18+'5'!H18+'6'!H18+'7'!H18+'8'!H18+'9'!H18+'10'!H18+'11'!H18+'12'!H18+'13'!H18+'14'!H18+'15'!H18+'16'!H18</f>
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="1"/>
-        <v>1993.575</v>
+        <v>1049.25</v>
       </c>
       <c r="J18" s="172">
         <f>+'1'!J18+'2'!J18+'4'!J18+'3'!J18+'5'!J18+'6'!J18+'7'!J18+'8'!J18+'9'!J18+'10'!J18+'11'!J18+'12'!J18+'13'!J18+'14'!J18+'15'!J18+'16'!J18+'17'!J18+'18'!J18</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18" s="172">
         <f>+'1'!K18+'2'!K18+'4'!K18+'3'!K18+'5'!K18+'6'!K18+'7'!K18+'8'!K18+'9'!K18+'10'!K18</f>
@@ -23663,23 +23663,23 @@
       </c>
       <c r="L18" s="175">
         <f>+'1'!L18+'2'!L18+'4'!L18+'3'!L18+'5'!L18+'6'!L18+'7'!L18+'8'!L18+'9'!L18+'10'!L18</f>
-        <v>159.48599999999999</v>
+        <v>83.94</v>
       </c>
       <c r="M18" s="118">
         <f t="shared" si="2"/>
-        <v>1834.0889999999999</v>
+        <v>965.31</v>
       </c>
       <c r="N18" s="101">
         <f>+'1'!N18+'2'!N18+'4'!N18+'3'!N18+'5'!N18+'6'!N18+'7'!N18+'8'!N18+'9'!N18+'10'!N18</f>
-        <v>389.73342000000002</v>
+        <v>223.90995000000001</v>
       </c>
       <c r="O18" s="101">
         <f>+'1'!O18+'2'!O18+'4'!O18+'3'!O18+'5'!O18+'6'!O18+'7'!O18+'8'!O18+'9'!O18+'10'!O18</f>
-        <v>31.811161500000004</v>
+        <v>5.9460997500000001</v>
       </c>
       <c r="P18" s="120">
         <f t="shared" si="0"/>
-        <v>2255.6335814999998</v>
+        <v>1195.16604975</v>
       </c>
       <c r="T18" s="163" t="str">
         <f>+'5'!A5</f>
@@ -23687,7 +23687,7 @@
       </c>
       <c r="U18" s="164">
         <f>+'5'!P35</f>
-        <v>6835.851936</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -23717,11 +23717,11 @@
       <c r="G19" s="114"/>
       <c r="H19" s="172">
         <f>+'1'!H19+'2'!H19+'4'!H19+'3'!H19+'5'!H19+'6'!H19+'7'!H19+'8'!H19+'9'!H19+'10'!H19+'11'!H19+'12'!H19+'13'!H19+'14'!H19+'15'!H19+'16'!H19</f>
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="1"/>
-        <v>2033.92</v>
+        <v>944.32</v>
       </c>
       <c r="J19" s="172">
         <f>+'1'!J19+'2'!J19+'4'!J19+'3'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19+'13'!J19+'14'!J19+'15'!J19+'16'!J19+'17'!J19+'18'!J19</f>
@@ -23733,23 +23733,23 @@
       </c>
       <c r="L19" s="175">
         <f>+'1'!L19+'2'!L19+'4'!L19+'3'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19</f>
-        <v>162.71359999999999</v>
+        <v>75.545600000000007</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="2"/>
-        <v>1871.2064</v>
+        <v>868.77440000000001</v>
       </c>
       <c r="N19" s="101">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>371.568128</v>
+        <v>191.130368</v>
       </c>
       <c r="O19" s="101">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>34.871267839999994</v>
+        <v>5.2995238400000009</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="0"/>
-        <v>2277.6457958400001</v>
+        <v>1065.20429184</v>
       </c>
       <c r="T19" s="163" t="str">
         <f>+'6'!A5</f>
@@ -23787,15 +23787,15 @@
       <c r="G20" s="114"/>
       <c r="H20" s="172">
         <f>+'1'!H20+'2'!H20+'4'!H20+'3'!H20+'5'!H20+'6'!H20+'7'!H20+'8'!H20+'9'!H20+'10'!H20+'11'!H20+'12'!H20+'13'!H20+'14'!H20+'15'!H20+'16'!H20</f>
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="1"/>
-        <v>2033.92</v>
+        <v>944.32</v>
       </c>
       <c r="J20" s="172">
         <f>+'1'!J20+'2'!J20+'4'!J20+'3'!J20+'5'!J20+'6'!J20+'7'!J20+'8'!J20+'9'!J20+'10'!J20+'11'!J20+'12'!J20+'13'!J20+'14'!J20+'15'!J20+'16'!J20+'17'!J20+'18'!J20</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K20" s="172">
         <f>+'1'!K20+'2'!K20+'4'!K20+'3'!K20+'5'!K20+'6'!K20+'7'!K20+'8'!K20+'9'!K20+'10'!K20</f>
@@ -23803,23 +23803,23 @@
       </c>
       <c r="L20" s="175">
         <f>+'1'!L20+'2'!L20+'4'!L20+'3'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20</f>
-        <v>162.71359999999999</v>
+        <v>75.545600000000007</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="2"/>
-        <v>1871.2064</v>
+        <v>868.77440000000001</v>
       </c>
       <c r="N20" s="101">
         <f>+'1'!N20+'2'!N20+'4'!N20+'3'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20</f>
-        <v>416.60492799999997</v>
+        <v>223.09196800000001</v>
       </c>
       <c r="O20" s="101">
         <f>+'1'!O20+'2'!O20+'4'!O20+'3'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20</f>
-        <v>35.357955839999995</v>
+        <v>5.4593318399999999</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="0"/>
-        <v>2323.1692838399999</v>
+        <v>1097.32569984</v>
       </c>
       <c r="T20" s="163" t="str">
         <f>+'7'!A5</f>
@@ -23857,15 +23857,15 @@
       <c r="G21" s="114"/>
       <c r="H21" s="172">
         <f>+'1'!H21+'2'!H21+'4'!H21+'3'!H21+'5'!H21+'6'!H21+'7'!H21+'8'!H21+'9'!H21+'10'!H21+'11'!H21+'12'!H21+'13'!H21+'14'!H21+'15'!H21+'16'!H21</f>
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="1"/>
-        <v>2106.56</v>
+        <v>1016.96</v>
       </c>
       <c r="J21" s="172">
         <f>+'1'!J21+'2'!J21+'4'!J21+'3'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21+'13'!J21+'14'!J21+'15'!J21+'16'!J21+'17'!J21+'18'!J21</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="172">
         <f>+'1'!K21+'2'!K21+'4'!K21+'3'!K21+'5'!K21+'6'!K21+'7'!K21+'8'!K21+'9'!K21+'10'!K21</f>
@@ -23873,23 +23873,23 @@
       </c>
       <c r="L21" s="175">
         <f>+'1'!L21+'2'!L21+'4'!L21+'3'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21</f>
-        <v>168.5248</v>
+        <v>81.356800000000007</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="2"/>
-        <v>1938.0352</v>
+        <v>935.60320000000002</v>
       </c>
       <c r="N21" s="101">
         <f>+'1'!N21+'2'!N21+'4'!N21+'3'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21</f>
-        <v>399.34566399999994</v>
+        <v>205.83270400000001</v>
       </c>
       <c r="O21" s="101">
         <f>+'1'!O21+'2'!O21+'4'!O21+'3'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21</f>
-        <v>35.605803519999995</v>
+        <v>5.7071795199999995</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="0"/>
-        <v>2372.9866675199996</v>
+        <v>1147.1430835199999</v>
       </c>
       <c r="T21" s="163" t="str">
         <f>+'8'!A5</f>
@@ -23951,15 +23951,15 @@
       </c>
       <c r="N22" s="101">
         <f>+'1'!N22+'2'!N22+'4'!N22+'3'!N22+'5'!N22+'6'!N22+'7'!N22+'8'!N22+'9'!N22+'10'!N22</f>
-        <v>473.81994000000009</v>
+        <v>416.38722000000007</v>
       </c>
       <c r="O22" s="101">
         <f>+'1'!O22+'2'!O22+'4'!O22+'3'!O22+'5'!O22+'6'!O22+'7'!O22+'8'!O22+'9'!O22+'10'!O22</f>
-        <v>13.137734700000003</v>
+        <v>12.850571100000003</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="0"/>
-        <v>2640.6846747</v>
+        <v>2582.9647911000002</v>
       </c>
       <c r="T22" s="163" t="str">
         <f>+'9'!A5</f>
@@ -24117,7 +24117,7 @@
       <c r="B25" s="210"/>
       <c r="C25" s="211">
         <f>H25/40</f>
-        <v>6.4749999999999996</v>
+        <v>4</v>
       </c>
       <c r="D25" s="205"/>
       <c r="E25" s="205"/>
@@ -24128,15 +24128,15 @@
       </c>
       <c r="H25" s="177">
         <f t="shared" si="3"/>
-        <v>259</v>
+        <v>160</v>
       </c>
       <c r="I25" s="178">
         <f t="shared" si="3"/>
-        <v>14508.924999999999</v>
+        <v>8407.1500000000015</v>
       </c>
       <c r="J25" s="177">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K25" s="178">
         <f t="shared" si="3"/>
@@ -24144,23 +24144,23 @@
       </c>
       <c r="L25" s="179">
         <f t="shared" si="3"/>
-        <v>1090.0999999999999</v>
+        <v>601.95800000000008</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="3"/>
-        <v>13336.442000000001</v>
+        <v>7722.8090000000011</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>2821.0956700000006</v>
+        <v>1667.4612099999999</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>214.17016515</v>
+        <v>46.951351050000007</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>16371.707835149999</v>
+        <v>9437.2215610499989</v>
       </c>
       <c r="T25" s="163" t="str">
         <f>+'12'!A5</f>
@@ -24290,7 +24290,7 @@
       </c>
       <c r="U30" s="165">
         <f>SUM(U14:U28)</f>
-        <v>16371.707835150002</v>
+        <v>9437.2215610500007</v>
       </c>
     </row>
     <row r="31" spans="1:21 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24323,7 +24323,7 @@
       <c r="O32" s="222"/>
       <c r="P32" s="152">
         <f>I25</f>
-        <v>14508.924999999999</v>
+        <v>8407.1500000000015</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24344,7 +24344,7 @@
       <c r="O33" s="224"/>
       <c r="P33" s="153">
         <f>L25</f>
-        <v>1090.0999999999999</v>
+        <v>601.95800000000008</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24387,7 +24387,7 @@
       <c r="O35" s="224"/>
       <c r="P35" s="153">
         <f>P32-P33-P34</f>
-        <v>13336.441999999999</v>
+        <v>7722.8090000000011</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24412,7 +24412,7 @@
       </c>
       <c r="P36" s="153">
         <f>N25</f>
-        <v>2821.0956700000006</v>
+        <v>1667.4612099999999</v>
       </c>
     </row>
     <row r="37" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24434,7 +24434,7 @@
       <c r="O37" s="226"/>
       <c r="P37" s="153">
         <f>P35+P36</f>
-        <v>16157.53767</v>
+        <v>9390.2702100000006</v>
       </c>
     </row>
     <row r="38" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24459,7 +24459,7 @@
       </c>
       <c r="P38" s="153">
         <f>O38*P37</f>
-        <v>403.93844175000004</v>
+        <v>234.75675525000003</v>
       </c>
     </row>
     <row r="39" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24469,7 +24469,7 @@
       <c r="O39" s="204"/>
       <c r="P39" s="160">
         <f>P37+P38</f>
-        <v>16561.476111749998</v>
+        <v>9625.026965250001</v>
       </c>
     </row>
     <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -26043,11 +26043,11 @@
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C12" s="77" t="str">
         <f>IF($O32&gt;21.99%,"No","Yes")</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
@@ -26068,7 +26068,7 @@
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="228"/>
       <c r="B13" s="168">
-        <v>0</v>
+        <v>3520225590257</v>
       </c>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
@@ -26156,7 +26156,7 @@
       <c r="M15" s="250"/>
       <c r="N15" s="92">
         <f>IF(B12="Registered",18%,22%)</f>
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="O15" s="93">
         <f>IF(B11="Filer",0.5%,2.5%)</f>
@@ -26216,15 +26216,15 @@
       </c>
       <c r="N16" s="106">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>106.1841</v>
+        <v>86.877899999999997</v>
       </c>
       <c r="O16" s="107">
         <f>(N16+M16)*$O$15</f>
-        <v>2.9441954999999997</v>
+        <v>2.8476644999999996</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="1">M16+N16+O16</f>
-        <v>591.78329549999989</v>
+        <v>572.38056449999988</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="XFD16" t="s">
@@ -26280,15 +26280,15 @@
       </c>
       <c r="N17" s="118">
         <f t="shared" si="0"/>
-        <v>117.72585000000001</v>
+        <v>96.321149999999989</v>
       </c>
       <c r="O17" s="119">
         <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
-        <v>3.0019042499999999</v>
+        <v>2.89488075</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="1"/>
-        <v>603.38275425000006</v>
+        <v>581.87103074999993</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -26566,15 +26566,15 @@
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>315.87996000000004</v>
+        <v>258.44724000000002</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>8.7584898000000013</v>
+        <v>8.4713262000000018</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>1760.4564498000002</v>
+        <v>1702.7365662000002</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26725,15 +26725,15 @@
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>539.78991000000008</v>
+        <v>441.64629000000002</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>14.704589550000001</v>
+        <v>14.213871450000001</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>2955.6224995500002</v>
+        <v>2856.98816145</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26868,11 +26868,11 @@
       </c>
       <c r="O32" s="156">
         <f>IF(B12="Registered",18%,22%)</f>
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>539.78991000000008</v>
+        <v>441.64629000000002</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26894,7 +26894,7 @@
       <c r="O33" s="226"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>2940.9179100000001</v>
+        <v>2842.7742900000003</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26919,7 +26919,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>14.704589550000001</v>
+        <v>14.213871450000001</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26929,7 +26929,7 @@
       <c r="O35" s="204"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>2955.6224995500002</v>
+        <v>2856.9881614500005</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -29874,12 +29874,10 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="100"/>
-      <c r="H16" s="101">
-        <v>18</v>
-      </c>
+      <c r="H16" s="101"/>
       <c r="I16" s="102">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>944.32499999999993</v>
+        <v>0</v>
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
@@ -29888,23 +29886,23 @@
       </c>
       <c r="L16" s="105">
         <f>I16*8%</f>
-        <v>75.545999999999992</v>
+        <v>0</v>
       </c>
       <c r="M16" s="106">
         <f>I16-K16-L16</f>
-        <v>868.779</v>
+        <v>0</v>
       </c>
       <c r="N16" s="106">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>156.38021999999998</v>
+        <v>0</v>
       </c>
       <c r="O16" s="107">
         <f>(N16+M16)*$O$15</f>
-        <v>25.628980500000001</v>
+        <v>0</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="1">M16+N16+O16</f>
-        <v>1050.7882004999999</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="XFD16" t="s">
@@ -29936,39 +29934,35 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="114"/>
-      <c r="H17" s="115">
-        <v>18</v>
-      </c>
+      <c r="H17" s="115"/>
       <c r="I17" s="116">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
-        <v>944.32499999999993</v>
-      </c>
-      <c r="J17" s="117">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J17" s="117"/>
       <c r="K17" s="1">
         <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
         <f t="shared" ref="L17:L21" si="4">I17*8%</f>
-        <v>75.545999999999992</v>
+        <v>0</v>
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="5">I17-K17-L17</f>
-        <v>868.779</v>
+        <v>0</v>
       </c>
       <c r="N17" s="118">
         <f t="shared" si="0"/>
-        <v>165.82346999999999</v>
+        <v>0</v>
       </c>
       <c r="O17" s="119">
         <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
-        <v>25.865061750000002</v>
+        <v>0</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="1"/>
-        <v>1060.46753175</v>
+        <v>0</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -30000,39 +29994,35 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="114"/>
-      <c r="H18" s="115">
-        <v>18</v>
-      </c>
+      <c r="H18" s="115"/>
       <c r="I18" s="116">
         <f t="shared" si="2"/>
-        <v>944.32499999999993</v>
-      </c>
-      <c r="J18" s="117">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J18" s="117"/>
       <c r="K18" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L18" s="105">
         <f t="shared" si="4"/>
-        <v>75.545999999999992</v>
+        <v>0</v>
       </c>
       <c r="M18" s="118">
         <f t="shared" si="5"/>
-        <v>868.779</v>
+        <v>0</v>
       </c>
       <c r="N18" s="118">
         <f t="shared" si="0"/>
-        <v>165.82346999999999</v>
+        <v>0</v>
       </c>
       <c r="O18" s="119">
         <f t="shared" si="6"/>
-        <v>25.865061750000002</v>
+        <v>0</v>
       </c>
       <c r="P18" s="120">
         <f t="shared" si="1"/>
-        <v>1060.46753175</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -30060,12 +30050,10 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="114"/>
-      <c r="H19" s="115">
-        <v>15</v>
-      </c>
+      <c r="H19" s="115"/>
       <c r="I19" s="116">
         <f t="shared" si="2"/>
-        <v>1089.5999999999999</v>
+        <v>0</v>
       </c>
       <c r="J19" s="117"/>
       <c r="K19" s="1">
@@ -30074,23 +30062,23 @@
       </c>
       <c r="L19" s="105">
         <f t="shared" si="4"/>
-        <v>87.167999999999992</v>
+        <v>0</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="5"/>
-        <v>1002.4319999999999</v>
+        <v>0</v>
       </c>
       <c r="N19" s="118">
         <f t="shared" si="0"/>
-        <v>180.43775999999997</v>
+        <v>0</v>
       </c>
       <c r="O19" s="119">
         <f t="shared" si="6"/>
-        <v>29.571743999999995</v>
+        <v>0</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="1"/>
-        <v>1212.4415039999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -30118,39 +30106,35 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="114"/>
-      <c r="H20" s="115">
-        <v>15</v>
-      </c>
+      <c r="H20" s="115"/>
       <c r="I20" s="116">
         <f t="shared" si="2"/>
-        <v>1089.5999999999999</v>
-      </c>
-      <c r="J20" s="117">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J20" s="117"/>
       <c r="K20" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L20" s="105">
         <f t="shared" si="4"/>
-        <v>87.167999999999992</v>
+        <v>0</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="5"/>
-        <v>1002.4319999999999</v>
+        <v>0</v>
       </c>
       <c r="N20" s="118">
         <f t="shared" si="0"/>
-        <v>193.51295999999996</v>
+        <v>0</v>
       </c>
       <c r="O20" s="119">
         <f t="shared" si="6"/>
-        <v>29.898623999999998</v>
+        <v>0</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="1"/>
-        <v>1225.8435839999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -30178,39 +30162,35 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="114"/>
-      <c r="H21" s="115">
-        <v>15</v>
-      </c>
+      <c r="H21" s="115"/>
       <c r="I21" s="116">
         <f t="shared" si="2"/>
-        <v>1089.5999999999999</v>
-      </c>
-      <c r="J21" s="117">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J21" s="117"/>
       <c r="K21" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L21" s="105">
         <f t="shared" si="4"/>
-        <v>87.167999999999992</v>
+        <v>0</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="5"/>
-        <v>1002.4319999999999</v>
+        <v>0</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>193.51295999999996</v>
+        <v>0</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="6"/>
-        <v>29.898623999999998</v>
+        <v>0</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="1"/>
-        <v>1225.8435839999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -30396,11 +30376,11 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>6101.7749999999996</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
@@ -30409,23 +30389,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>488.142</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>5613.6329999999998</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>1055.4908399999999</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>166.72809599999999</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>6835.8519359999991</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -30475,7 +30455,7 @@
       <c r="O28" s="222"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>6101.7749999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30496,7 +30476,7 @@
       <c r="O29" s="224"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>488.142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30539,7 +30519,7 @@
       <c r="O31" s="224"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>5613.6329999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30564,7 +30544,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>1055.4908399999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30586,7 +30566,7 @@
       <c r="O33" s="226"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>6669.1238400000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -30611,7 +30591,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>166.72809600000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -30621,7 +30601,7 @@
       <c r="O35" s="204"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>6835.851936</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
